--- a/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.8</t>
+    <t>0.1.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:55:04-06:00</t>
+    <t>2025-09-19T15:08:00-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1781,17 +1781,17 @@
   <dimension ref="A1:AO61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="65.52734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.18359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.91796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.30859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="163.74609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="146.8515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1800,27 +1800,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="120.87890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.01953125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.46484375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="108.41015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.7265625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.7734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="98.36328125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="20.26171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="248.7734375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="88.21484375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="18.171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.10</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T15:08:00-05:00</t>
+    <t>2026-04-23T10:10:52-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -436,7 +436,7 @@
     <t>MedicationAdministration.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -474,7 +474,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -664,7 +664,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -3112,7 +3112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>151</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>244</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>250</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>279</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>305</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>315</v>
       </c>
@@ -6257,7 +6257,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>336</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>372</v>
       </c>
@@ -7181,7 +7181,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>379</v>
       </c>
@@ -8928,12 +8928,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO61">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2278" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T15:08:00-05:00</t>
+    <t>2026-06-10T07:35:08-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,9 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}mcode-reason-required:One of reasonCode or reasonReference SHALL be present {reasonCode.exists() or reasonReference.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}mcode-reason-required:One of reasonCode or reasonReference SHALL be present {reasonCode.exists() or reasonReference.exists()}termination-reason-code-invariant:When status is stopped, only certain statusReason values are allowed {status = 'stopped' and statusReason.exists() and statusReason.coding.exists() implies statusReason.coding.exists(system = 'http://snomed.info/sct' and (code = '182992009' or code = '266721009' or code = '407563006' or code = '160932005' or code = '105480006' or code = '184081006' or code = '309846006' or code = '399307001' or code = '419620001' or code = '7058009' or code = '443729008' or code = '77386006'))}termination-reason-invariant:Certain statusReason values are allowed only when status is stopped {statusReason.exists() and statusReason.coding.exists(
+      system = 'http://snomed.info/sct' and (code = '182992009' or code = '266721009' or code = '407563006' or code = '160932005' or
+ code = '105480006' or code = '184081006' or code = '309846006' or code = '399307001' or  code = '419620001' or code = '7058009' or code = '443729008' or code = '77386006')) implies status = 'stopped'}</t>
   </si>
   <si>
     <t>Event</t>
@@ -436,7 +438,7 @@
     <t>MedicationAdministration.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -474,7 +476,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -664,7 +666,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -793,20 +795,20 @@
 </t>
   </si>
   <si>
-    <t>MedicationAdministration.extension:terminationReason</t>
-  </si>
-  <si>
-    <t>terminationReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-treatment-termination-reason}
+    <t>MedicationAdministration.extension:normalizationBasis</t>
+  </si>
+  <si>
+    <t>normalizationBasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-normalization-basis}
 </t>
   </si>
   <si>
-    <t>Treatment Termination Reason Extension</t>
-  </si>
-  <si>
-    <t>A code explaining the unplanned or premature termination, or normal completion, of a plan of treatment, course of medication, or research study.</t>
+    <t>Normalization Basis Extension</t>
+  </si>
+  <si>
+    <t>The method (e.g., body weight, body surface area, flat dose, age) used to normalize the medication dosage.</t>
   </si>
   <si>
     <t>MedicationAdministration.modifierExtension</t>
@@ -930,10 +932,7 @@
     <t>A code indicating why the administration was not performed.</t>
   </si>
   <si>
-    <t>A set of codes indicating the reason why the MedicationAdministration is negated.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/us/mcode/ValueSet/mcode-treatment-termination-reason-vs</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -1197,7 +1196,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-primary-cancer-condition|http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-secondary-cancer-condition)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-condition-problems-health-concerns)
 </t>
   </si>
   <si>
@@ -1783,7 +1782,7 @@
   <cols>
     <col min="1" max="1" width="58.765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.91796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.30859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.05078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -1791,7 +1790,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="146.8515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="84.62890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1806,7 +1805,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="108.41015625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.7265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.70703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -3112,7 +3111,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>151</v>
       </c>
@@ -4750,7 +4749,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>244</v>
       </c>
@@ -4885,10 +4884,10 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -5450,7 +5449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>279</v>
       </c>
@@ -5567,7 +5566,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>290</v>
       </c>
@@ -5586,7 +5585,7 @@
         <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -5628,13 +5627,11 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="Y33" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="Y33" s="2"/>
+      <c r="Z33" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
@@ -5667,16 +5664,16 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5684,10 +5681,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5713,10 +5710,10 @@
         <v>291</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5746,11 +5743,11 @@
         <v>220</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5767,7 +5764,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5785,24 +5782,24 @@
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AM34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5825,16 +5822,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5864,7 +5861,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5882,7 +5879,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5897,27 +5894,27 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AO35" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" hidden="true">
-      <c r="A36" t="s" s="2">
-        <v>315</v>
-      </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5940,13 +5937,13 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5997,7 +5994,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>87</v>
@@ -6012,16 +6009,16 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6029,10 +6026,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6055,13 +6052,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6112,7 +6109,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6127,16 +6124,16 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6144,10 +6141,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6170,13 +6167,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6227,7 +6224,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6245,24 +6242,24 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" hidden="true">
-      <c r="A39" t="s" s="2">
-        <v>336</v>
-      </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6285,13 +6282,13 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6342,7 +6339,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>87</v>
@@ -6357,16 +6354,16 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6374,10 +6371,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6400,13 +6397,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6457,7 +6454,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6472,16 +6469,16 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6489,10 +6486,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6604,10 +6601,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6721,14 +6718,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6750,10 +6747,10 @@
         <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>111</v>
@@ -6808,7 +6805,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6840,10 +6837,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6869,10 +6866,10 @@
         <v>291</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6902,11 +6899,11 @@
         <v>207</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6923,7 +6920,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6938,10 +6935,10 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -6955,10 +6952,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6981,13 +6978,13 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7038,7 +7035,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>87</v>
@@ -7053,27 +7050,27 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>372</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7099,10 +7096,10 @@
         <v>291</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7133,7 +7130,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7151,7 +7148,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7166,27 +7163,27 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AO46" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>379</v>
-      </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7209,16 +7206,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7268,7 +7265,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7283,27 +7280,27 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7326,16 +7323,16 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7385,7 +7382,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7400,16 +7397,16 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -7417,10 +7414,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7443,13 +7440,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7500,7 +7497,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7518,13 +7515,13 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -7532,10 +7529,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7558,13 +7555,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7615,7 +7612,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7630,10 +7627,10 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
@@ -7647,10 +7644,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7673,13 +7670,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7730,7 +7727,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7742,13 +7739,13 @@
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -7762,10 +7759,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7877,10 +7874,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7994,14 +7991,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8023,10 +8020,10 @@
         <v>108</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>111</v>
@@ -8081,7 +8078,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8113,10 +8110,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8142,10 +8139,10 @@
         <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8196,7 +8193,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8214,7 +8211,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -8228,10 +8225,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8257,13 +8254,13 @@
         <v>291</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8292,11 +8289,11 @@
         <v>207</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8313,7 +8310,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8331,13 +8328,13 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8345,10 +8342,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8374,10 +8371,10 @@
         <v>291</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8407,11 +8404,11 @@
         <v>207</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8428,7 +8425,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8446,13 +8443,13 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -8460,10 +8457,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8489,13 +8486,13 @@
         <v>291</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8524,11 +8521,11 @@
         <v>207</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8545,7 +8542,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8563,13 +8560,13 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -8577,10 +8574,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8603,16 +8600,16 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8662,7 +8659,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8680,13 +8677,13 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -8694,10 +8691,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8720,16 +8717,16 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8779,7 +8776,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8797,13 +8794,13 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
@@ -8811,10 +8808,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8837,16 +8834,16 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8896,7 +8893,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8914,7 +8911,7 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
@@ -8928,12 +8925,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO61">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:35:08-05:00</t>
+    <t>2026-06-11T12:11:14-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T12:11:14-05:00</t>
+    <t>2026-06-12T09:38:46-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:38:46-05:00</t>
+    <t>2026-06-21T22:38:39-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T22:38:39-05:00</t>
+    <t>2026-06-21T23:16:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T23:16:04-05:00</t>
+    <t>2026-06-22T08:51:47-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:51:47-05:00</t>
+    <t>2026-06-22T09:21:59-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:21:59-05:00</t>
+    <t>2026-06-25T19:24:07-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T19:24:07-05:00</t>
+    <t>2026-08-19T10:07:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-medication-administration.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2278" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.10</t>
+    <t>0.1.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T10:10:52-05:00</t>
+    <t>2026-08-27T20:01:54-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>
@@ -269,7 +269,9 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}mcode-reason-required:One of reasonCode or reasonReference SHALL be present {reasonCode.exists() or reasonReference.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}mcode-reason-required:One of reasonCode or reasonReference SHALL be present {reasonCode.exists() or reasonReference.exists()}termination-reason-code-invariant:When status is stopped, only certain statusReason values are allowed {status = 'stopped' and statusReason.exists() and statusReason.coding.exists() implies statusReason.coding.exists(system = 'http://snomed.info/sct' and (code = '182992009' or code = '266721009' or code = '407563006' or code = '160932005' or code = '105480006' or code = '184081006' or code = '309846006' or code = '399307001' or code = '419620001' or code = '7058009' or code = '443729008' or code = '77386006'))}termination-reason-invariant:Certain statusReason values are allowed only when status is stopped {statusReason.exists() and statusReason.coding.exists(
+      system = 'http://snomed.info/sct' and (code = '182992009' or code = '266721009' or code = '407563006' or code = '160932005' or
+ code = '105480006' or code = '184081006' or code = '309846006' or code = '399307001' or  code = '419620001' or code = '7058009' or code = '443729008' or code = '77386006')) implies status = 'stopped'}</t>
   </si>
   <si>
     <t>Event</t>
@@ -793,20 +795,20 @@
 </t>
   </si>
   <si>
-    <t>MedicationAdministration.extension:terminationReason</t>
-  </si>
-  <si>
-    <t>terminationReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-treatment-termination-reason}
+    <t>MedicationAdministration.extension:normalizationBasis</t>
+  </si>
+  <si>
+    <t>normalizationBasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-normalization-basis}
 </t>
   </si>
   <si>
-    <t>Treatment Termination Reason Extension</t>
-  </si>
-  <si>
-    <t>A code explaining the unplanned or premature termination, or normal completion, of a plan of treatment, course of medication, or research study.</t>
+    <t>Normalization Basis Extension</t>
+  </si>
+  <si>
+    <t>The method (e.g., body weight, body surface area, flat dose, age) used to normalize the medication dosage.</t>
   </si>
   <si>
     <t>MedicationAdministration.modifierExtension</t>
@@ -930,10 +932,7 @@
     <t>A code indicating why the administration was not performed.</t>
   </si>
   <si>
-    <t>A set of codes indicating the reason why the MedicationAdministration is negated.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/us/mcode/ValueSet/mcode-treatment-termination-reason-vs</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -1197,7 +1196,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-primary-cancer-condition|http://hl7.org/fhir/us/mcode/StructureDefinition/mcode-secondary-cancer-condition)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-condition-problems-health-concerns)
 </t>
   </si>
   <si>
@@ -1783,7 +1782,7 @@
   <cols>
     <col min="1" max="1" width="58.765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.91796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.30859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.05078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -1791,7 +1790,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="146.8515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="84.62890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1806,7 +1805,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="108.41015625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.7265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.70703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -4867,7 +4866,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>250</v>
       </c>
@@ -4885,10 +4884,10 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -5567,7 +5566,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>290</v>
       </c>
@@ -5586,7 +5585,7 @@
         <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -5628,13 +5627,11 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="Y33" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="Y33" s="2"/>
+      <c r="Z33" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
@@ -5667,16 +5664,16 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5684,10 +5681,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5713,10 +5710,10 @@
         <v>291</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5746,11 +5743,11 @@
         <v>220</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5767,7 +5764,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5785,7 +5782,7 @@
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
@@ -5799,10 +5796,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5825,16 +5822,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5864,7 +5861,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5882,7 +5879,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5897,16 +5894,16 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -5914,10 +5911,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5940,13 +5937,13 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5997,7 +5994,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>87</v>
@@ -6012,16 +6009,16 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6029,10 +6026,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6055,13 +6052,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6112,7 +6109,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6127,16 +6124,16 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6144,10 +6141,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6170,13 +6167,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6227,7 +6224,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6245,10 +6242,10 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6259,10 +6256,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6285,13 +6282,13 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6342,7 +6339,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>87</v>
@@ -6357,16 +6354,16 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6374,10 +6371,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6400,13 +6397,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6457,7 +6454,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6472,16 +6469,16 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6489,10 +6486,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6604,10 +6601,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6721,14 +6718,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6750,10 +6747,10 @@
         <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>111</v>
@@ -6808,7 +6805,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6840,10 +6837,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6869,10 +6866,10 @@
         <v>291</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6902,11 +6899,11 @@
         <v>207</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6923,7 +6920,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6938,10 +6935,10 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -6955,10 +6952,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6981,13 +6978,13 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7038,7 +7035,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>87</v>
@@ -7053,10 +7050,10 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -7070,10 +7067,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7099,10 +7096,10 @@
         <v>291</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7133,7 +7130,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7151,7 +7148,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7166,16 +7163,16 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -7183,10 +7180,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7209,16 +7206,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7268,7 +7265,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7283,27 +7280,27 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7326,16 +7323,16 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7385,7 +7382,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7400,16 +7397,16 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -7417,10 +7414,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7443,13 +7440,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7500,7 +7497,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7518,13 +7515,13 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>21</v>
@@ -7532,10 +7529,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7558,13 +7555,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7615,7 +7612,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7630,10 +7627,10 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
@@ -7647,10 +7644,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7673,13 +7670,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7730,7 +7727,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7742,13 +7739,13 @@
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -7762,10 +7759,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7877,10 +7874,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7994,14 +7991,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8023,10 +8020,10 @@
         <v>108</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>111</v>
@@ -8081,7 +8078,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8113,10 +8110,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8142,10 +8139,10 @@
         <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8196,7 +8193,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8214,7 +8211,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -8228,10 +8225,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8257,13 +8254,13 @@
         <v>291</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8292,11 +8289,11 @@
         <v>207</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8313,7 +8310,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8331,13 +8328,13 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8345,10 +8342,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8374,10 +8371,10 @@
         <v>291</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8407,11 +8404,11 @@
         <v>207</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8428,7 +8425,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8446,13 +8443,13 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -8460,10 +8457,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8489,13 +8486,13 @@
         <v>291</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8524,11 +8521,11 @@
         <v>207</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8545,7 +8542,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8563,13 +8560,13 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -8577,10 +8574,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8603,16 +8600,16 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8662,7 +8659,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8680,13 +8677,13 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -8694,10 +8691,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8720,16 +8717,16 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8779,7 +8776,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8797,13 +8794,13 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
@@ -8811,10 +8808,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8837,16 +8834,16 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8896,7 +8893,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8914,7 +8911,7 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
